--- a/Team-Data/2008-09/1-20-2008-09.xlsx
+++ b/Team-Data/2008-09/1-20-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>8.1</v>
       </c>
       <c r="M2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N2" t="n">
         <v>0.374</v>
       </c>
       <c r="O2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P2" t="n">
         <v>24.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
         <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="U2" t="n">
         <v>21.5</v>
@@ -718,40 +785,40 @@
         <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF2" t="n">
         <v>8</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>23</v>
@@ -772,10 +839,10 @@
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -784,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -802,7 +869,7 @@
         <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -811,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.786</v>
+        <v>0.791</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="K3" t="n">
         <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="O3" t="n">
         <v>20.9</v>
       </c>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
         <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>23.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -951,7 +1018,7 @@
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
@@ -966,10 +1033,10 @@
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>21</v>
@@ -1136,7 +1203,7 @@
         <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1145,7 +1212,7 @@
         <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1157,7 +1224,7 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -1210,79 +1277,79 @@
         <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.405</v>
+        <v>0.429</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
         <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.373</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0.798</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S5" t="n">
         <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
         <v>4</v>
@@ -1291,7 +1358,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1300,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1312,28 +1379,28 @@
         <v>19</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>13</v>
@@ -1345,7 +1412,7 @@
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
         <v>26</v>
@@ -1360,7 +1427,7 @@
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -1389,100 +1456,100 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101</v>
+        <v>100.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,34 +1558,34 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="n">
         <v>20</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>17</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1530,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>16</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>26</v>
@@ -1697,16 +1764,16 @@
         <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -1753,58 +1820,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.651</v>
+        <v>0.643</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M8" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="O8" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="P8" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="Q8" t="n">
         <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
         <v>41</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.6</v>
@@ -1819,19 +1886,19 @@
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>104</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,7 +1910,7 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>10</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
         <v>24</v>
@@ -1903,10 +1970,10 @@
         <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
@@ -2031,7 +2098,7 @@
         <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>16</v>
@@ -2055,7 +2122,7 @@
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
         <v>14</v>
@@ -2070,10 +2137,10 @@
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2088,7 +2155,7 @@
         <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2280,7 @@
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
         <v>17</v>
@@ -2258,7 +2325,7 @@
         <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2450,10 @@
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2395,7 +2462,7 @@
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2419,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
@@ -2428,10 +2495,10 @@
         <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>21</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
         <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.357</v>
+        <v>0.366</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>39.3</v>
       </c>
       <c r="J12" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
         <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.2</v>
+        <v>104.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2571,16 +2638,16 @@
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
@@ -2589,19 +2656,19 @@
         <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
@@ -2619,22 +2686,22 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2768,7 +2835,7 @@
         <v>24</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
         <v>30</v>
@@ -2777,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>25</v>
@@ -2789,7 +2856,7 @@
         <v>18</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.795</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,7 +2930,7 @@
         <v>39.8</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
@@ -2872,34 +2939,34 @@
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.379</v>
+        <v>0.384</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="P14" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
@@ -2911,28 +2978,28 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2962,16 +3029,16 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,13 +3050,13 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>28</v>
@@ -3144,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3317,25 +3384,25 @@
         <v>12</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
@@ -3347,10 +3414,10 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3362,7 +3429,7 @@
         <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.465</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.446</v>
@@ -3418,37 +3485,37 @@
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P17" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R17" t="n">
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="T17" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
@@ -3457,16 +3524,16 @@
         <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3478,10 +3545,10 @@
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3490,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3502,10 +3569,10 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
@@ -3514,10 +3581,10 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3526,13 +3593,13 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3544,7 +3611,7 @@
         <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J18" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M18" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R18" t="n">
         <v>12.6</v>
@@ -3627,7 +3694,7 @@
         <v>20.2</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
         <v>6.5</v>
@@ -3636,22 +3703,22 @@
         <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC18" t="n">
         <v>-3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3681,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3699,13 +3766,13 @@
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-3</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3842,10 +3909,10 @@
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3860,7 +3927,7 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
         <v>9</v>
@@ -3875,10 +3942,10 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
@@ -3902,7 +3969,7 @@
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4051,7 +4118,7 @@
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4075,13 +4142,13 @@
         <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
         <v>15</v>
@@ -4090,7 +4157,7 @@
         <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-3.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
@@ -4245,7 +4312,7 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4467,7 @@
         <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>16</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4445,7 +4512,7 @@
         <v>22</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4561,25 +4628,25 @@
         <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1</v>
       </c>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
@@ -4609,13 +4676,13 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>12</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4773,13 +4840,13 @@
         <v>29</v>
       </c>
       <c r="AN24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4791,7 +4858,7 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4806,10 +4873,10 @@
         <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -4931,10 +4998,10 @@
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4949,10 +5016,10 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN25" t="n">
         <v>4</v>
@@ -4985,7 +5052,7 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -4997,7 +5064,7 @@
         <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -5029,109 +5096,109 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0.625</v>
+        <v>0.61</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>21</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>22</v>
-      </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>10</v>
@@ -5140,13 +5207,13 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>14</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>13</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5167,22 +5234,22 @@
         <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.238</v>
+        <v>0.244</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
@@ -5232,16 +5299,16 @@
         <v>81.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M27" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.339</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
         <v>20.1</v>
@@ -5250,22 +5317,22 @@
         <v>25.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R27" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T27" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
         <v>6.7</v>
@@ -5274,34 +5341,34 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB27" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
@@ -5316,28 +5383,28 @@
         <v>20</v>
       </c>
       <c r="AM27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
         <v>21</v>
@@ -5361,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -5393,73 +5460,73 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="H28" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I28" t="n">
         <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
         <v>0.397</v>
       </c>
       <c r="O28" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.756</v>
       </c>
       <c r="R28" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="S28" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T28" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="U28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V28" t="n">
         <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA28" t="n">
         <v>18.6</v>
@@ -5468,10 +5535,10 @@
         <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,13 +5550,13 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5498,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5510,16 +5577,16 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
         <v>7</v>
@@ -5546,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
         <v>22</v>
@@ -5668,13 +5735,13 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
         <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>18</v>
@@ -5689,7 +5756,7 @@
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5722,13 +5789,13 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.595</v>
+        <v>0.585</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,7 +5842,7 @@
         <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.476</v>
@@ -5790,13 +5857,13 @@
         <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P30" t="n">
         <v>27.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.777</v>
+        <v>0.773</v>
       </c>
       <c r="R30" t="n">
         <v>11.8</v>
@@ -5808,13 +5875,13 @@
         <v>41.3</v>
       </c>
       <c r="U30" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="V30" t="n">
         <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X30" t="n">
         <v>4.9</v>
@@ -5823,31 +5890,31 @@
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="AC30" t="n">
         <v>3.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
       </c>
       <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
         <v>11</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>12</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>14</v>
@@ -5910,7 +5977,7 @@
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6059,7 +6126,7 @@
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>30</v>
@@ -6068,7 +6135,7 @@
         <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-20-2008-09</t>
+          <t>2009-01-20</t>
         </is>
       </c>
     </row>
